--- a/Result/profitability/6482.xlsx
+++ b/Result/profitability/6482.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM50"/>
+  <dimension ref="A1:AM51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6784,6 +6784,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>6482</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>96</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>95</v>
+      </c>
+      <c r="F51" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="G51" t="n">
+        <v>11</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>11.08%</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>9</v>
+      </c>
+      <c r="K51" t="n">
+        <v>5</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.6849999999999999</v>
+      </c>
+      <c r="N51" t="n">
+        <v>98.51625000000001</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W51" t="n">
+        <v>-0.09000000000000002</v>
+      </c>
+      <c r="X51" t="n">
+        <v>-0.3214285714285715</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0.04999999999999716</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0.0005068423720222537</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.689999999999998</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.01742088444490264</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK51" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
